--- a/docs/import-examples/ejemplo-movimientos.xlsx
+++ b/docs/import-examples/ejemplo-movimientos.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Movimientos" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Cómo leer este ejemplo" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="93">
   <si>
     <t>Fecha</t>
   </si>
@@ -31,10 +32,10 @@
     <t>Tipo</t>
   </si>
   <si>
-    <t>03/01/2025</t>
-  </si>
-  <si>
-    <t>Sueldo mensual</t>
+    <t>Nota (se ignora al importar)</t>
+  </si>
+  <si>
+    <t>Sueldo agosto</t>
   </si>
   <si>
     <t>Trabajo</t>
@@ -46,28 +47,139 @@
     <t>Ingreso</t>
   </si>
   <si>
-    <t>06/01/2025</t>
-  </si>
-  <si>
-    <t>Venta bicicleta</t>
+    <t>Ingreso con Tipo explícito y fecha como celda de fecha de Excel</t>
+  </si>
+  <si>
+    <t>02/08/2026</t>
+  </si>
+  <si>
+    <t>Alquiler agosto</t>
+  </si>
+  <si>
+    <t>Hogar</t>
+  </si>
+  <si>
+    <t>Alquiler</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>08/01/2025</t>
-  </si>
-  <si>
-    <t>Alquiler</t>
-  </si>
-  <si>
-    <t>Hogar</t>
-  </si>
-  <si>
-    <t>09/01/2025</t>
-  </si>
-  <si>
-    <t>Ropa nueva</t>
+    <t>Sin Tipo: el monto negativo lo marca como gasto. Fecha escrita como texto dd/mm/aaaa</t>
+  </si>
+  <si>
+    <t>05/08/2026</t>
+  </si>
+  <si>
+    <t>Compra semanal</t>
+  </si>
+  <si>
+    <t>Comestibles</t>
+  </si>
+  <si>
+    <t>Super</t>
+  </si>
+  <si>
+    <t>-58.340,75</t>
+  </si>
+  <si>
+    <t>Monto escrito como texto, con punto de miles y coma decimal</t>
+  </si>
+  <si>
+    <t>09/08/2026</t>
+  </si>
+  <si>
+    <t>Carga de nafta</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>12/08/2026</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>Edenor</t>
+  </si>
+  <si>
+    <t>Gasto</t>
+  </si>
+  <si>
+    <t>Monto positivo pero Tipo = Gasto: el Tipo manda sobre el signo</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
+  </si>
+  <si>
+    <t>Cena con amigos</t>
+  </si>
+  <si>
+    <t>Entretenimiento</t>
+  </si>
+  <si>
+    <t>Etiqueta vacía: se usa la Descripción ("Cena con amigos")</t>
+  </si>
+  <si>
+    <t>23/08/2026</t>
+  </si>
+  <si>
+    <t>Venta de la bici</t>
+  </si>
+  <si>
+    <t>Venta usada</t>
+  </si>
+  <si>
+    <t>Categoría vacía: va a "Otros". Sin Tipo y positivo: ingreso</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Sueldo septiembre</t>
+  </si>
+  <si>
+    <t>Fecha en formato aaaa-mm-dd: también se acepta</t>
+  </si>
+  <si>
+    <t>Alquiler septiembre</t>
+  </si>
+  <si>
+    <t>Misma etiqueta que en agosto: se reutiliza, no se duplica</t>
+  </si>
+  <si>
+    <t>Alimento balanceado</t>
+  </si>
+  <si>
+    <t>Mascotas</t>
+  </si>
+  <si>
+    <t>Veterinaria</t>
+  </si>
+  <si>
+    <t>Categoría que no existe: se crea sola al importar</t>
+  </si>
+  <si>
+    <t>Proyecto freelance</t>
+  </si>
+  <si>
+    <t>Freelance</t>
+  </si>
+  <si>
+    <t>$ 350.000</t>
+  </si>
+  <si>
+    <t>Monto con signo $: se ignora el símbolo</t>
+  </si>
+  <si>
+    <t>Zapatillas</t>
   </si>
   <si>
     <t>Compras</t>
@@ -76,89 +188,120 @@
     <t>Ropa</t>
   </si>
   <si>
-    <t>Gasto</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
-  </si>
-  <si>
-    <t>Supermercado</t>
-  </si>
-  <si>
-    <t>Comestibles</t>
-  </si>
-  <si>
-    <t>Super</t>
-  </si>
-  <si>
-    <t>11/01/2025</t>
-  </si>
-  <si>
-    <t>Nafta</t>
-  </si>
-  <si>
-    <t>Transporte</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>12/01/2025</t>
-  </si>
-  <si>
-    <t>Luz y gas</t>
-  </si>
-  <si>
-    <t>Servicios</t>
-  </si>
-  <si>
-    <t>13/01/2025</t>
+    <t>Monto con decimales</t>
+  </si>
+  <si>
+    <t>Cuota gimnasio</t>
+  </si>
+  <si>
+    <t>Deportes</t>
+  </si>
+  <si>
+    <t>Gimnasio</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>Farmacia</t>
+  </si>
+  <si>
+    <t>Descripción vacía: queda "Sin descripción" y se ve la Etiqueta</t>
+  </si>
+  <si>
+    <t>Sueldo octubre</t>
+  </si>
+  <si>
+    <t>Alquiler octubre</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>Fibertel</t>
+  </si>
+  <si>
+    <t>Corte de pelo</t>
+  </si>
+  <si>
+    <t>Belleza</t>
+  </si>
+  <si>
+    <t>Peluquería</t>
+  </si>
+  <si>
+    <t>SUBE</t>
+  </si>
+  <si>
+    <t>Colectivo</t>
+  </si>
+  <si>
+    <t>Reintegro tarjeta</t>
+  </si>
+  <si>
+    <t>Reintegro</t>
+  </si>
+  <si>
+    <t>Un reintegro también es ingreso, aunque sea en una categoría de gastos</t>
+  </si>
+  <si>
+    <t>Entradas al cine</t>
   </si>
   <si>
     <t>Cine</t>
   </si>
   <si>
-    <t>Entretenimiento</t>
-  </si>
-  <si>
-    <t>14/01/2025</t>
-  </si>
-  <si>
-    <t>Cuota gimnasio</t>
-  </si>
-  <si>
-    <t>Deportes</t>
-  </si>
-  <si>
-    <t>Gimnasio</t>
-  </si>
-  <si>
-    <t>15/01/2025</t>
-  </si>
-  <si>
-    <t>Farmacia</t>
-  </si>
-  <si>
-    <t>Salud</t>
-  </si>
-  <si>
-    <t>16/01/2025</t>
-  </si>
-  <si>
-    <t>Peluquería</t>
-  </si>
-  <si>
-    <t>Belleza</t>
+    <t>Cómo leer este ejemplo</t>
+  </si>
+  <si>
+    <t>Tres meses de movimientos (agosto a octubre de 2026). Cada fila muestra una forma válida de cargar los datos; la columna gris "Nota" explica cuál.</t>
+  </si>
+  <si>
+    <t>Columnas</t>
+  </si>
+  <si>
+    <t>• Fecha (obligatoria): dd/mm/aaaa, aaaa-mm-dd o una celda con formato de fecha de Excel.</t>
+  </si>
+  <si>
+    <t>• Descripción: texto libre. Vacía → "Sin descripción".</t>
+  </si>
+  <si>
+    <t>• Categoría: si ya la tenés, se usa; si no existe, se crea. Vacía → "Otros".</t>
+  </si>
+  <si>
+    <t>• Etiqueta: agrupa movimientos parecidos (Super, Alquiler...). Vacía → se usa la Descripción.</t>
+  </si>
+  <si>
+    <t>• Monto (obligatorio): número o texto. Acepta 1.234,56 · $ 12.500 · -45000. No puede ser 0.</t>
+  </si>
+  <si>
+    <t>• Tipo: Ingreso o Gasto. Vacío → decide el signo del Monto (negativo = gasto). Si lo completás, manda sobre el signo.</t>
+  </si>
+  <si>
+    <t>Para tener en cuenta</t>
+  </si>
+  <si>
+    <t>• La hoja tiene que llamarse "Movimientos". El orden de las columnas no importa.</t>
+  </si>
+  <si>
+    <t>• Las columnas que no reconocemos (como "Nota") se ignoran: podés dejarlas o borrarlas.</t>
+  </si>
+  <si>
+    <t>• Si subís el mismo archivo dos veces, se importa dos veces. Si te equivocás, podés deshacer la última migración desde Importar.</t>
+  </si>
+  <si>
+    <t>• Hasta 1000 filas por archivo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;-#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -167,15 +310,32 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+    </font>
+    <font>
       <b/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF6B7280"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F0E3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -190,11 +350,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,36 +707,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="2" max="6" width="22" customWidth="1"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="72" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46235</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -574,211 +755,619 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>1500000</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-420000</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-35000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2">
+        <v>32500</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-27000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="2">
+        <v>90000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>25000</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="G9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D10" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E10" s="2">
+        <v>-420000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-61200</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-24800</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-89999.9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-18000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="2">
+        <v>-14350</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
         <v>15</v>
       </c>
-      <c r="E4">
-        <v>-350000</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E18" s="2">
+        <v>-420000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-21900</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C20" t="s">
         <v>20</v>
       </c>
-      <c r="E5">
-        <v>-45000</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6">
-        <v>-60000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="E20" s="2">
+        <v>-64780</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="2">
+        <v>-16000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7">
-        <v>-30000</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8">
-        <v>-25000</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9">
-        <v>-8000</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2">
+        <v>-10000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10">
-        <v>-15000</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11">
-        <v>-12000</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12">
-        <v>-18000</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="2">
+        <v>-19000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
